--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_67625_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_67625_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R28c826ffde4c4866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R66ef44aae0e34355"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1050.6424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.7771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    876.3769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    938.1775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_67625_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_67625_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R66ef44aae0e34355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rafca1c61493848ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1333.8059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1408.2028</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1645.8947</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1982.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1305.8352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    988.7014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1140.3968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1362.1341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1558.0668</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1551.9006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1311.4007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1570.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1626.8385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1982.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1614.2058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2008.0858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2930.6770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1240.1642</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1385.0540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1570.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1684.3933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1278.2220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1658.6703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1749.7016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2520.4115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1084.9963</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1031.3262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1192.2624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1620.5150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2653.2789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2397.6404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1031.3262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.2344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    929.1772</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    970.1288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.2388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    863.4986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    842.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    867.7771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.2388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1224.0682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1402.3942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1171.3445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1328.1831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1245.5581</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1652.2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>18/08/2026</x:t>
         </x:is>
       </x:c>
